--- a/Results/Phase 2/Methanol/methanol eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Methanol/methanol eutrophication terrestrial results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003925158878183389</v>
+        <v>0.003637117552051409</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004268809413821119</v>
+        <v>0.004194247515591294</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00387599318386175</v>
+        <v>0.00358693644575216</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004043445458557742</v>
+        <v>0.003930749026895133</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003693817982227366</v>
+        <v>0.003478096405266485</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00385939138954403</v>
+        <v>0.003592688982209173</v>
       </c>
       <c r="H33" t="n">
-        <v>0.003818846114037725</v>
+        <v>0.003547507864264865</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003992205335797087</v>
+        <v>0.003652387655475253</v>
       </c>
       <c r="J33" t="n">
-        <v>0.003892928784005532</v>
+        <v>0.003606379548351371</v>
       </c>
       <c r="K33" t="n">
-        <v>0.004442516094910635</v>
+        <v>0.003919086798165794</v>
       </c>
       <c r="L33" t="n">
-        <v>0.003920626966847127</v>
+        <v>0.003622599372270767</v>
       </c>
       <c r="M33" t="n">
-        <v>0.005497502159863265</v>
+        <v>0.004524258877483313</v>
       </c>
       <c r="N33" t="n">
-        <v>0.00409767669189304</v>
+        <v>0.003722280600029252</v>
       </c>
       <c r="O33" t="n">
-        <v>0.007755925915483806</v>
+        <v>0.00749579371461474</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003772595454155642</v>
+        <v>0.00354173120666091</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003624306478714933</v>
+        <v>0.00344259280377948</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003693560140113099</v>
+        <v>0.003477831021161962</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003833347521846924</v>
+        <v>0.003576395582115073</v>
       </c>
       <c r="T33" t="n">
-        <v>0.004011684781349736</v>
+        <v>0.003665149397829401</v>
       </c>
       <c r="U33" t="n">
-        <v>0.006955050675922018</v>
+        <v>0.006531091870150578</v>
       </c>
       <c r="V33" t="n">
-        <v>0.003579310918091133</v>
+        <v>0.003424539234354291</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005987238020757385</v>
+        <v>0.005749509457507985</v>
       </c>
       <c r="X33" t="n">
-        <v>0.00363247581789334</v>
+        <v>0.003446527219181054</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003711346749469632</v>
+        <v>0.003496806404757654</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.005438498158112651</v>
+        <v>0.005267735890796007</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.004114660622337675</v>
+        <v>0.003734824176422331</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.004399833982570457</v>
+        <v>0.003879513469958589</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.00309927384652057</v>
+        <v>0.003073182898864715</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003845441437094622</v>
+        <v>0.00379301895218803</v>
       </c>
       <c r="D33" t="n">
-        <v>0.003153878968075897</v>
+        <v>0.003104319770179343</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003755352848315998</v>
+        <v>0.003721330970497946</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00323383339021572</v>
+        <v>0.003150982499876838</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003189646479190861</v>
+        <v>0.003129431673858198</v>
       </c>
       <c r="H33" t="n">
-        <v>0.003181134470788299</v>
+        <v>0.003118296577737131</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003175804045340279</v>
+        <v>0.003116442721984891</v>
       </c>
       <c r="J33" t="n">
-        <v>0.003223816394569231</v>
+        <v>0.003148228836980546</v>
       </c>
       <c r="K33" t="n">
-        <v>0.003235252861599547</v>
+        <v>0.003155727086996794</v>
       </c>
       <c r="L33" t="n">
-        <v>0.003357683731944011</v>
+        <v>0.003232204337011494</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003184339791291686</v>
+        <v>0.003121868363721319</v>
       </c>
       <c r="N33" t="n">
-        <v>0.003226540904197061</v>
+        <v>0.003146855100351966</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006938986742554597</v>
+        <v>0.006836643622278205</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003232742598573332</v>
+        <v>0.003156204676317116</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003140607280884458</v>
+        <v>0.003097307253684111</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003440993308204795</v>
+        <v>0.003269439041787573</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003280615196054988</v>
+        <v>0.003185571732458082</v>
       </c>
       <c r="T33" t="n">
-        <v>0.003223574552508952</v>
+        <v>0.00314424843135352</v>
       </c>
       <c r="U33" t="n">
-        <v>0.00505203172068381</v>
+        <v>0.004988598878134151</v>
       </c>
       <c r="V33" t="n">
-        <v>0.003229839523680158</v>
+        <v>0.00315408233439245</v>
       </c>
       <c r="W33" t="n">
-        <v>0.004875884039644303</v>
+        <v>0.004738643162910399</v>
       </c>
       <c r="X33" t="n">
-        <v>0.003713791018214219</v>
+        <v>0.003441100852553255</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003455756471183139</v>
+        <v>0.003282706945169309</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004922191834188549</v>
+        <v>0.004865876186086503</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.003450123465363</v>
+        <v>0.003279841752445758</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.00310460648984441</v>
+        <v>0.003074080244054117</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003737065562506631</v>
+        <v>0.003507838002254386</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004217960623212836</v>
+        <v>0.004143868176779497</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00372766378053088</v>
+        <v>0.003484442359180168</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003993720575526541</v>
+        <v>0.003891730818472195</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003463284221108941</v>
+        <v>0.003330170806448136</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003779462781283898</v>
+        <v>0.003530313734564552</v>
       </c>
       <c r="H33" t="n">
-        <v>0.003445420810156613</v>
+        <v>0.003317442864767112</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003638543046497638</v>
+        <v>0.003431239585896095</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00382013217447903</v>
+        <v>0.003547433450325747</v>
       </c>
       <c r="K33" t="n">
-        <v>0.004177670393493145</v>
+        <v>0.003764048748204655</v>
       </c>
       <c r="L33" t="n">
-        <v>0.003798928973061859</v>
+        <v>0.00353450763296002</v>
       </c>
       <c r="M33" t="n">
-        <v>0.005258725899227477</v>
+        <v>0.004372246013188147</v>
       </c>
       <c r="N33" t="n">
-        <v>0.003790060320363711</v>
+        <v>0.003525229439601807</v>
       </c>
       <c r="O33" t="n">
-        <v>0.007464130248937256</v>
+        <v>0.007265395772043181</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003799680131758034</v>
+        <v>0.003543411784624182</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003484910631860762</v>
+        <v>0.003345162559151915</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003457628640990044</v>
+        <v>0.003325490803080644</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003765788519965437</v>
+        <v>0.003521565443818705</v>
       </c>
       <c r="T33" t="n">
-        <v>0.003751482708511019</v>
+        <v>0.003498451109388967</v>
       </c>
       <c r="U33" t="n">
-        <v>0.00654044778756897</v>
+        <v>0.006190112257180557</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0033950866499924</v>
+        <v>0.003298619811612945</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005889659303090163</v>
+        <v>0.005612630542547886</v>
       </c>
       <c r="X33" t="n">
-        <v>0.003660473492700191</v>
+        <v>0.003447425554457413</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00361590487479541</v>
+        <v>0.003425488341133168</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.005266079582354119</v>
+        <v>0.005131344441123208</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.003860328281412559</v>
+        <v>0.003569827918964629</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.004308972062492875</v>
+        <v>0.003810790812144887</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003605256338083365</v>
+        <v>0.003423265562872985</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004189522148926159</v>
+        <v>0.004126906484713412</v>
       </c>
       <c r="D33" t="n">
-        <v>0.003818512574067379</v>
+        <v>0.003536447472662789</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004002751189984235</v>
+        <v>0.003895053542713135</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003443019246167192</v>
+        <v>0.003317013163827715</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003730027594693535</v>
+        <v>0.003500130549592403</v>
       </c>
       <c r="H33" t="n">
-        <v>0.003346063546392209</v>
+        <v>0.003257949738685458</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003802580209630741</v>
+        <v>0.003524570350751915</v>
       </c>
       <c r="J33" t="n">
-        <v>0.003778205334001355</v>
+        <v>0.003520722110625858</v>
       </c>
       <c r="K33" t="n">
-        <v>0.003876281030348014</v>
+        <v>0.00358828083603032</v>
       </c>
       <c r="L33" t="n">
-        <v>0.003675070074930468</v>
+        <v>0.003459136996620581</v>
       </c>
       <c r="M33" t="n">
-        <v>0.004976117146926876</v>
+        <v>0.004205168318595969</v>
       </c>
       <c r="N33" t="n">
-        <v>0.003570142227886513</v>
+        <v>0.003393272110112943</v>
       </c>
       <c r="O33" t="n">
-        <v>0.007284772075196926</v>
+        <v>0.007133683502634788</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003763977823420757</v>
+        <v>0.003521192470326671</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003438663232955212</v>
+        <v>0.003316965019066578</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003344173982991654</v>
+        <v>0.003257812814148566</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003703877034534278</v>
+        <v>0.003482922656801418</v>
       </c>
       <c r="T33" t="n">
-        <v>0.003657269628949176</v>
+        <v>0.003441069450294118</v>
       </c>
       <c r="U33" t="n">
-        <v>0.006281797131343427</v>
+        <v>0.006040982112905688</v>
       </c>
       <c r="V33" t="n">
-        <v>0.003438380537299147</v>
+        <v>0.00332416302919548</v>
       </c>
       <c r="W33" t="n">
-        <v>0.00580939929018137</v>
+        <v>0.005569956294684547</v>
       </c>
       <c r="X33" t="n">
-        <v>0.003784907305228045</v>
+        <v>0.003518836838708702</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003911834933600826</v>
+        <v>0.003599214421725597</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.005239757591028372</v>
+        <v>0.005115122582942958</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.003862124677004908</v>
+        <v>0.003568270160533281</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.004218275405233917</v>
+        <v>0.003755737809049327</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003498591086395055</v>
+        <v>0.003346570925386179</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003915676870142467</v>
+        <v>0.003860084763728742</v>
       </c>
       <c r="D33" t="n">
-        <v>0.003553297545325963</v>
+        <v>0.003370080992999385</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003908682330975038</v>
+        <v>0.003838082155791931</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003446057179833315</v>
+        <v>0.003304283571009676</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003631062327516398</v>
+        <v>0.003429120067693013</v>
       </c>
       <c r="H33" t="n">
-        <v>0.003304186790767576</v>
+        <v>0.003218294367151371</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003716828268507917</v>
+        <v>0.003461857307325607</v>
       </c>
       <c r="J33" t="n">
-        <v>0.003691235236732334</v>
+        <v>0.003457290011294441</v>
       </c>
       <c r="K33" t="n">
-        <v>0.003962553104873359</v>
+        <v>0.003626646983636719</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0035706504078213</v>
+        <v>0.003385822199306282</v>
       </c>
       <c r="M33" t="n">
-        <v>0.004599596367460079</v>
+        <v>0.003985711601052395</v>
       </c>
       <c r="N33" t="n">
-        <v>0.003392685341497793</v>
+        <v>0.003273642532544764</v>
       </c>
       <c r="O33" t="n">
-        <v>0.007212173571937545</v>
+        <v>0.007068588719037732</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003650932074379871</v>
+        <v>0.003441866054862682</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003383175154560714</v>
+        <v>0.003270612920090971</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003406192964650246</v>
+        <v>0.003278101577504397</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003628348798665783</v>
+        <v>0.00342419347676663</v>
       </c>
       <c r="T33" t="n">
-        <v>0.003659540848452034</v>
+        <v>0.003427004237670618</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005577885137942351</v>
+        <v>0.005348093360631264</v>
       </c>
       <c r="V33" t="n">
-        <v>0.003516595308608571</v>
+        <v>0.003359912461967825</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005018337671656454</v>
+        <v>0.004863221460638883</v>
       </c>
       <c r="X33" t="n">
-        <v>0.003792195771408584</v>
+        <v>0.00351271609491131</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.004248717345375235</v>
+        <v>0.003779989950755554</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.005146973416344769</v>
+        <v>0.005043830136273102</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.003882750877740602</v>
+        <v>0.003564710221618511</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.004087374381644094</v>
+        <v>0.003668492224113047</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003227657546828545</v>
+        <v>0.003169717752266844</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004039019349005772</v>
+        <v>0.004011630645616758</v>
       </c>
       <c r="D33" t="n">
-        <v>0.003417756098010822</v>
+        <v>0.00327708851789323</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003875291851155045</v>
+        <v>0.003798438453746738</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003235960216647009</v>
+        <v>0.003170490488133329</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003290942550128484</v>
+        <v>0.003210532211586326</v>
       </c>
       <c r="H33" t="n">
-        <v>0.003393043500466831</v>
+        <v>0.003259079325439561</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003374591579821361</v>
+        <v>0.003250822320663958</v>
       </c>
       <c r="J33" t="n">
-        <v>0.003362527690857482</v>
+        <v>0.003251212813030486</v>
       </c>
       <c r="K33" t="n">
-        <v>0.003579522138028526</v>
+        <v>0.003381796645115859</v>
       </c>
       <c r="L33" t="n">
-        <v>0.003500860703214125</v>
+        <v>0.003340367704864033</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003778936314895529</v>
+        <v>0.003500476629705999</v>
       </c>
       <c r="N33" t="n">
-        <v>0.003502204535206091</v>
+        <v>0.003330970673387066</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006907898228797719</v>
+        <v>0.00683663640434052</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003398086217788378</v>
+        <v>0.003273474269640366</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003353647941523863</v>
+        <v>0.00324301154603532</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003416486886344699</v>
+        <v>0.003273381598685731</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003360535820674236</v>
+        <v>0.003256754765631544</v>
       </c>
       <c r="T33" t="n">
-        <v>0.003297707298300089</v>
+        <v>0.003208109373503442</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005914960680540517</v>
+        <v>0.005772030897531686</v>
       </c>
       <c r="V33" t="n">
-        <v>0.003218198753097674</v>
+        <v>0.003163876192891806</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005520006245429056</v>
+        <v>0.005345944310415634</v>
       </c>
       <c r="X33" t="n">
-        <v>0.003449682127891316</v>
+        <v>0.003296919722469727</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003231525276270994</v>
+        <v>0.003169433592924176</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.005101829657848895</v>
+        <v>0.00500366935103061</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.003481619533167805</v>
+        <v>0.003317866356765006</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.003419212041937711</v>
+        <v>0.003276091981097311</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003197786354283243</v>
+        <v>0.003147970383435472</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004104124618663238</v>
+        <v>0.004050467260705711</v>
       </c>
       <c r="D33" t="n">
-        <v>0.003192229832254203</v>
+        <v>0.003142508288019568</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003909260625295185</v>
+        <v>0.003816151391380006</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003305771479096893</v>
+        <v>0.003209380638870829</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003244353887596158</v>
+        <v>0.003179081147281826</v>
       </c>
       <c r="H33" t="n">
-        <v>0.003281617643319299</v>
+        <v>0.003192150894953152</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003273566208573067</v>
+        <v>0.003189627808360815</v>
       </c>
       <c r="J33" t="n">
-        <v>0.003275150232451872</v>
+        <v>0.003195672689159683</v>
       </c>
       <c r="K33" t="n">
-        <v>0.003218634247689015</v>
+        <v>0.003159650621810132</v>
       </c>
       <c r="L33" t="n">
-        <v>0.00329230009244946</v>
+        <v>0.003210929352690806</v>
       </c>
       <c r="M33" t="n">
-        <v>0.00317508282982666</v>
+        <v>0.003132683283302739</v>
       </c>
       <c r="N33" t="n">
-        <v>0.003304841325352427</v>
+        <v>0.003210927466948952</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006937760536891924</v>
+        <v>0.006848309630903952</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003286003337754995</v>
+        <v>0.003202509849437935</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003167830012418573</v>
+        <v>0.003129444781327329</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003489983722021457</v>
+        <v>0.00331503648095356</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003282643788544163</v>
+        <v>0.003203695637830213</v>
       </c>
       <c r="T33" t="n">
-        <v>0.003205844417169259</v>
+        <v>0.00315067272504245</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005647304001457745</v>
+        <v>0.005614586192981781</v>
       </c>
       <c r="V33" t="n">
-        <v>0.00327141115964885</v>
+        <v>0.003194748783974618</v>
       </c>
       <c r="W33" t="n">
-        <v>0.00550310462331681</v>
+        <v>0.005346304208546304</v>
       </c>
       <c r="X33" t="n">
-        <v>0.00371432075763439</v>
+        <v>0.003457803670311538</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00327577434773535</v>
+        <v>0.003192201622494402</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.005093867562494764</v>
+        <v>0.00499555084575518</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.003389476049605893</v>
+        <v>0.003259902304673459</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.003122510435823244</v>
+        <v>0.003100360518715705</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003228873506612145</v>
+        <v>0.003152956914023457</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003865841082680595</v>
+        <v>0.003805096671379315</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00318778744745403</v>
+        <v>0.003124564821745654</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00395660438113245</v>
+        <v>0.003846840535076197</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003239866434106244</v>
+        <v>0.003154165933078915</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003160145784486267</v>
+        <v>0.003111193907509656</v>
       </c>
       <c r="H33" t="n">
-        <v>0.003177231795585508</v>
+        <v>0.003116341966773394</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003163319280522658</v>
+        <v>0.003109194246703455</v>
       </c>
       <c r="J33" t="n">
-        <v>0.003218301624340398</v>
+        <v>0.003145485557855672</v>
       </c>
       <c r="K33" t="n">
-        <v>0.003143210181912901</v>
+        <v>0.00309853948334753</v>
       </c>
       <c r="L33" t="n">
-        <v>0.003284884576301369</v>
+        <v>0.003190023305059221</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003130089905851087</v>
+        <v>0.003090004415854504</v>
       </c>
       <c r="N33" t="n">
-        <v>0.003204780666625189</v>
+        <v>0.003135222246428499</v>
       </c>
       <c r="O33" t="n">
-        <v>0.007070972934462376</v>
+        <v>0.006927611614894131</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003295029456999549</v>
+        <v>0.003195104020861005</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003124722379086035</v>
+        <v>0.003087932097648465</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003460913712053691</v>
+        <v>0.003281539440662714</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003233190632930194</v>
+        <v>0.003156502309722554</v>
       </c>
       <c r="T33" t="n">
-        <v>0.003146685827159377</v>
+        <v>0.003099839977999745</v>
       </c>
       <c r="U33" t="n">
-        <v>0.004973195369850469</v>
+        <v>0.004936933246444447</v>
       </c>
       <c r="V33" t="n">
-        <v>0.003253434011013267</v>
+        <v>0.00316869809586036</v>
       </c>
       <c r="W33" t="n">
-        <v>0.004879179531793204</v>
+        <v>0.00474027631419465</v>
       </c>
       <c r="X33" t="n">
-        <v>0.003807620990212337</v>
+        <v>0.003501875046739802</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003228372193637477</v>
+        <v>0.003148537685209952</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.00500176403749664</v>
+        <v>0.004920911714452953</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.003373248295447869</v>
+        <v>0.003234913364033228</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.003115922041504613</v>
+        <v>0.003080906348069064</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003522079631768014</v>
+        <v>0.003370824046291084</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004138324577138203</v>
+        <v>0.004090300331799777</v>
       </c>
       <c r="D33" t="n">
-        <v>0.003591571429167204</v>
+        <v>0.00339913853680781</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003947366065536588</v>
+        <v>0.003859263800333042</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003395155087151173</v>
+        <v>0.003285073621480605</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003730358835539681</v>
+        <v>0.003500253212047702</v>
       </c>
       <c r="H33" t="n">
-        <v>0.003429144012897271</v>
+        <v>0.003301980948508139</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003664302701891608</v>
+        <v>0.003441351190232133</v>
       </c>
       <c r="J33" t="n">
-        <v>0.003734145138183729</v>
+        <v>0.003495917141209856</v>
       </c>
       <c r="K33" t="n">
-        <v>0.003870870963624695</v>
+        <v>0.003579910836988941</v>
       </c>
       <c r="L33" t="n">
-        <v>0.003735470987474798</v>
+        <v>0.003495403082732528</v>
       </c>
       <c r="M33" t="n">
-        <v>0.005120579555795834</v>
+        <v>0.004323010591692098</v>
       </c>
       <c r="N33" t="n">
-        <v>0.003903857059615894</v>
+        <v>0.003586458342523834</v>
       </c>
       <c r="O33" t="n">
-        <v>0.00724316357831139</v>
+        <v>0.007101499091661894</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003703418039980198</v>
+        <v>0.00347927607589343</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003467887625089125</v>
+        <v>0.003330829256991619</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003543220513658411</v>
+        <v>0.003368636258125172</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003586723434887418</v>
+        <v>0.003413283385428028</v>
       </c>
       <c r="T33" t="n">
-        <v>0.003623954429389479</v>
+        <v>0.003418194025247398</v>
       </c>
       <c r="U33" t="n">
-        <v>0.006298434244848428</v>
+        <v>0.006027651713687391</v>
       </c>
       <c r="V33" t="n">
-        <v>0.003347265375957895</v>
+        <v>0.003263623636498856</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005593268904752403</v>
+        <v>0.005415984370286258</v>
       </c>
       <c r="X33" t="n">
-        <v>0.003758052541764893</v>
+        <v>0.003498756856960735</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00356086981138723</v>
+        <v>0.003387077314076981</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.005258809847789358</v>
+        <v>0.005122621579080283</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.003769496238018122</v>
+        <v>0.003510163055557598</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.00414019415372171</v>
+        <v>0.003708909784606555</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003169443796410205</v>
+        <v>0.003139104596179771</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004132095939017102</v>
+        <v>0.004076650953051483</v>
       </c>
       <c r="D33" t="n">
-        <v>0.003251256589788944</v>
+        <v>0.003185738387185993</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003857959701377908</v>
+        <v>0.003792523298799862</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003285382838759228</v>
+        <v>0.003205749569686271</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003642319894133093</v>
+        <v>0.00343594748612929</v>
       </c>
       <c r="H33" t="n">
-        <v>0.003267605063630621</v>
+        <v>0.00319271584873961</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003274763924752258</v>
+        <v>0.003198433161188337</v>
       </c>
       <c r="J33" t="n">
-        <v>0.003429674699812825</v>
+        <v>0.003298931351745359</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00335903177009521</v>
+        <v>0.003254522474752046</v>
       </c>
       <c r="L33" t="n">
-        <v>0.003573374562651034</v>
+        <v>0.003388325620748802</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003363087395557858</v>
+        <v>0.003254317661109588</v>
       </c>
       <c r="N33" t="n">
-        <v>0.003356846935427066</v>
+        <v>0.003248164258541561</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006920828832437312</v>
+        <v>0.006851110899660668</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003499308050572579</v>
+        <v>0.003342076028187141</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.00329731558501069</v>
+        <v>0.003216583040487258</v>
       </c>
       <c r="R33" t="n">
-        <v>0.003511813230558009</v>
+        <v>0.003334659077807141</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003379444986490432</v>
+        <v>0.003270344969177311</v>
       </c>
       <c r="T33" t="n">
-        <v>0.003300696056508835</v>
+        <v>0.003214208700435477</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005760892371700855</v>
+        <v>0.005696229426716064</v>
       </c>
       <c r="V33" t="n">
-        <v>0.003256920840213191</v>
+        <v>0.003193490814988708</v>
       </c>
       <c r="W33" t="n">
-        <v>0.005558689024981599</v>
+        <v>0.005388100473600335</v>
       </c>
       <c r="X33" t="n">
-        <v>0.003720609737120098</v>
+        <v>0.003465361892963122</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003767148530514363</v>
+        <v>0.003494347206802564</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004996210620692792</v>
+        <v>0.004932937296729168</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.003354490786687203</v>
+        <v>0.003247872295039008</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.003758269015708011</v>
+        <v>0.003477115495814587</v>
       </c>
     </row>
   </sheetData>
